--- a/Price_List_Our_vs_Market_HS25E1112W1.xlsx
+++ b/Price_List_Our_vs_Market_HS25E1112W1.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K84"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -3352,44 +3352,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Machine</v>
-      </c>
-      <c r="C85" t="str">
-        <v>R32ELD-380V</v>
-      </c>
-      <c r="D85" t="str">
-        <v>Tube swaging machine, crimp 1/4"-2" 6-51mm 4SH, 12 die sets, 4kW, 380V 3ph, 310kg</v>
-      </c>
-      <c r="E85" t="str">
-        <v>1/4"-2"</v>
-      </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
-      <c r="G85" t="str">
-        <v>Unit</v>
-      </c>
-      <c r="H85" t="str">
-        <v>ON ORDER</v>
-      </c>
-      <c r="I85">
-        <v>653310</v>
-      </c>
-      <c r="J85" t="str">
-        <v/>
-      </c>
-      <c r="K85" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K85"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K84"/>
   </ignoredErrors>
 </worksheet>
 </file>